--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59890300-3DD2-42E1-B2CB-C16691465032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9ABC05-3037-47B2-9C65-47A113D19BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 19-12-2025'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 29-01-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9ABC05-3037-47B2-9C65-47A113D19BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F7F4F6-0D4E-4DCA-8559-AA2A574F84DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 29-01-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-02-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F7F4F6-0D4E-4DCA-8559-AA2A574F84DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66164BEC-591A-4415-A201-50784F8693EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-02-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 20-02-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -548,9 +548,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -655,7 +655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -690,7 +690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -725,7 +725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -768,7 +768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -803,7 +803,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -838,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -873,7 +873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -908,7 +908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -943,7 +943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66164BEC-591A-4415-A201-50784F8693EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1B5E88-005B-401B-82A1-54FCDB2B5675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 20-02-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 04-03-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1B5E88-005B-401B-82A1-54FCDB2B5675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B6EA91-6C7D-4861-9FD4-CD62D7B760AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 04-03-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 06-03-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B6EA91-6C7D-4861-9FD4-CD62D7B760AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E2FE8B-9FE2-465A-A745-BD15509C16CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E2FE8B-9FE2-465A-A745-BD15509C16CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BD13A1-E1DC-42F8-AFD2-C05042257A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BD13A1-E1DC-42F8-AFD2-C05042257A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD80A8A5-6794-4676-AD35-059571A50DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 06-03-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-03-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD80A8A5-6794-4676-AD35-059571A50DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D394CA4A-8515-44D7-97DF-798125F0A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D394CA4A-8515-44D7-97DF-798125F0A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1633CF4-14F5-497F-9AC5-4E1EFA780B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-03-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 11-03-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1633CF4-14F5-497F-9AC5-4E1EFA780B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8707A99E-62EA-41C8-9F51-B1099D1310E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8707A99E-62EA-41C8-9F51-B1099D1310E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591182EF-4152-484C-8A19-D584F41DE54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 11-03-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 20-03-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591182EF-4152-484C-8A19-D584F41DE54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7105BF5B-70A9-4C82-8440-845F382187C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 20-03-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 25-03-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7105BF5B-70A9-4C82-8440-845F382187C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C8BAD1-FC4B-4067-9481-804831BD6D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 25-03-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 08-04-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C8BAD1-FC4B-4067-9481-804831BD6D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023EADBA-716E-4E78-99EA-EDEF55DC9743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 08-04-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 10-04-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023EADBA-716E-4E78-99EA-EDEF55DC9743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB781F2-2B8B-4651-B008-B75CDCA897D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB781F2-2B8B-4651-B008-B75CDCA897D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F97D75-6511-498A-A41D-1C9347945ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 10-04-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 14-04-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -684,7 +684,7 @@
         <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
         <v>14</v>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F97D75-6511-498A-A41D-1C9347945ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D58C5E8-B90B-4C9A-BF26-13AE6EB23D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 14-04-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 24-04-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D58C5E8-B90B-4C9A-BF26-13AE6EB23D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F2C076-03CE-4C44-8E3C-41690CFEEE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F2C076-03CE-4C44-8E3C-41690CFEEE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF728D51-33F9-4DA2-A101-8BA7A5E0B645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 24-04-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 27-04-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF728D51-33F9-4DA2-A101-8BA7A5E0B645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BFC75D-4D22-484C-ADFD-C9C6FD924071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 27-04-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 06-05-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BFC75D-4D22-484C-ADFD-C9C6FD924071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827BE942-91FA-4CB2-AA7D-E59F35F0751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 06-05-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 01-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827BE942-91FA-4CB2-AA7D-E59F35F0751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7CF322-9B81-4606-A8C5-163C3D311D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 01-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7CF322-9B81-4606-A8C5-163C3D311D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDACA2F-5C61-4600-8C5E-15A959C88E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDACA2F-5C61-4600-8C5E-15A959C88E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD030CF8-807F-448B-ACE4-629A29F81E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 05-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9ABC05-3037-47B2-9C65-47A113D19BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA813FE-56D6-48D0-A351-3C2CE6FC7041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234C85E3-0DD4-4C3F-8573-DF0578C582D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D865C-A44A-43EF-AA5B-C3D24D749E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D865C-A44A-43EF-AA5B-C3D24D749E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3C697D-CB63-41AC-BB12-7373A9FF28B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3C697D-CB63-41AC-BB12-7373A9FF28B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3218779F-53E4-4E88-A202-6B5BD33E0C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 15-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -548,9 +548,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -655,7 +655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -690,7 +690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -725,7 +725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -768,7 +768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -803,7 +803,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -838,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -873,7 +873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -908,7 +908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -943,7 +943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3218779F-53E4-4E88-A202-6B5BD33E0C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258C3CCD-2E54-4523-8A68-6C4DAA5E364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 15-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 22-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258C3CCD-2E54-4523-8A68-6C4DAA5E364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03647ACC-8F87-4719-8CC0-CE81642D5472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 22-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 23-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -548,9 +548,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -620,7 +620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -655,7 +655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -690,7 +690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -725,7 +725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -768,7 +768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -803,7 +803,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -838,7 +838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -873,7 +873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -908,7 +908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -943,7 +943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03647ACC-8F87-4719-8CC0-CE81642D5472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1760471E-0230-4E97-A70E-393555ECE125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258C3CCD-2E54-4523-8A68-6C4DAA5E364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9F72E2-8E27-4590-AB2B-D1091418D9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 22-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 23-06-2026'!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9F72E2-8E27-4590-AB2B-D1091418D9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8797C0D9-ACD7-43B2-85C8-C2AA08B8DFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 23-06-2026'!$A$1:$K$25</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 25-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="88">
   <si>
     <t>Standard</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Clinea _Privath__ (EG)</t>
   </si>
   <si>
+    <t>Clinio _Privath__ (Clinio Medical)</t>
+  </si>
+  <si>
     <t>EPM _Privath__ (Metodika)</t>
   </si>
   <si>
@@ -58,15 +61,30 @@
     <t>XMO _Privath__ (CGM)</t>
   </si>
   <si>
+    <t>Binær dokumenttransport</t>
+  </si>
+  <si>
+    <t>BIN01 (B0131X)</t>
+  </si>
+  <si>
+    <t>Sende</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Henvisningsbilag</t>
+  </si>
+  <si>
+    <t>BIN02 (B0210X)</t>
+  </si>
+  <si>
     <t>Negativ kvittering</t>
   </si>
   <si>
     <t>CTL02 (C0230Q)</t>
   </si>
   <si>
-    <t>Sende</t>
-  </si>
-  <si>
     <t>Godkendt</t>
   </si>
   <si>
@@ -85,15 +103,18 @@
     <t>Ikke Godkendt</t>
   </si>
   <si>
-    <t>Tester</t>
-  </si>
-  <si>
     <t>Ambulantepikrise</t>
   </si>
   <si>
     <t>DIS02 (D0234L)</t>
   </si>
   <si>
+    <t>Skadestueepikrise</t>
+  </si>
+  <si>
+    <t>DIS03 (D0334L)</t>
+  </si>
+  <si>
     <t>Billeddiagnostisk epikrise</t>
   </si>
   <si>
@@ -142,6 +163,9 @@
     <t>REF06 (H0630R)</t>
   </si>
   <si>
+    <t>REF06 (H0631R)</t>
+  </si>
+  <si>
     <t>Fysioterapihenvisning</t>
   </si>
   <si>
@@ -160,6 +184,12 @@
     <t>SUP (3.0)</t>
   </si>
   <si>
+    <t>Den gode VANSEnvelope</t>
+  </si>
+  <si>
+    <t>VANSEnvelope (1.0)</t>
+  </si>
+  <si>
     <t>BinaryLetter</t>
   </si>
   <si>
@@ -172,6 +202,42 @@
     <t>XBIN02 (XB0210X)</t>
   </si>
   <si>
+    <t>NegativeReceipt</t>
+  </si>
+  <si>
+    <t>XCTL02 (XC0230Q)</t>
+  </si>
+  <si>
+    <t>PositiveReceipt</t>
+  </si>
+  <si>
+    <t>XCTL03 (XC0330Q)</t>
+  </si>
+  <si>
+    <t>DischargeLetter</t>
+  </si>
+  <si>
+    <t>XDIS01 (XD0134L)</t>
+  </si>
+  <si>
+    <t>OutPatientDischargeLetter</t>
+  </si>
+  <si>
+    <t>XDIS02 (XD0234L)</t>
+  </si>
+  <si>
+    <t>CasualtyWardLetter</t>
+  </si>
+  <si>
+    <t>XDIS03 (XD0334L)</t>
+  </si>
+  <si>
+    <t>RadiologyReport</t>
+  </si>
+  <si>
+    <t>XDIS05 (XD0533L)</t>
+  </si>
+  <si>
     <t>PhysiotherapiLetter</t>
   </si>
   <si>
@@ -184,6 +250,18 @@
     <t>XDIS13 (XD1333L)</t>
   </si>
   <si>
+    <t>ReportOfDischarge</t>
+  </si>
+  <si>
+    <t>XDIS18 (XD1834C)</t>
+  </si>
+  <si>
+    <t>ProgressOfCarePlan</t>
+  </si>
+  <si>
+    <t>XDIS21 (XD2134C)</t>
+  </si>
+  <si>
     <t>HospitalReferral</t>
   </si>
   <si>
@@ -200,6 +278,9 @@
   </si>
   <si>
     <t>XREF06 (XH0630R)</t>
+  </si>
+  <si>
+    <t>XREF06 (XH0631R)</t>
   </si>
   <si>
     <t>Physiotherapistreferral</t>
@@ -547,10 +628,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -584,113 +665,77 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -698,34 +743,37 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -733,448 +781,472 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
         <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
         <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1182,16 +1254,13 @@
         <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1199,16 +1268,37 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1216,13 +1306,37 @@
         <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>20</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1230,13 +1344,224 @@
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8797C0D9-ACD7-43B2-85C8-C2AA08B8DFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB9C21D-DB28-418F-B8AD-831166BA13FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 25-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 30-06-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB9C21D-DB28-418F-B8AD-831166BA13FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39F9C67-8AC8-4209-A32C-AE2022C26FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39F9C67-8AC8-4209-A32C-AE2022C26FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A17F9A-BC34-4396-83CB-615D83EE7172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 30-06-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 01-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A17F9A-BC34-4396-83CB-615D83EE7172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E059C6F1-601F-413C-BBF3-D9875C7FD5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 01-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A17F9A-BC34-4396-83CB-615D83EE7172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D316935-73B2-4D0A-8247-1536370B2615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 01-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 03-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E059C6F1-601F-413C-BBF3-D9875C7FD5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44633B4A-6C16-426B-88B4-630F510A907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 03-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44633B4A-6C16-426B-88B4-630F510A907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5E3AD-1CFD-4541-8EDE-51765EFEA67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 03-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-07-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5E3AD-1CFD-4541-8EDE-51765EFEA67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5786D1BB-003C-43CD-9CE9-4534ED2235B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-07-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 19-08-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5786D1BB-003C-43CD-9CE9-4534ED2235B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3661B1-4722-4994-BACE-61045585FAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 19-08-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 21-08-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3661B1-4722-4994-BACE-61045585FAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22DB2A4-FB62-4659-A204-6B45C1725E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 21-08-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 27-08-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22DB2A4-FB62-4659-A204-6B45C1725E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EA355A-CFBF-41E9-9725-32A774AD9162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 27-08-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EA355A-CFBF-41E9-9725-32A774AD9162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B581CE53-8D55-4E11-BF3D-E8AEC51BCD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 06-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B581CE53-8D55-4E11-BF3D-E8AEC51BCD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E87CD1-5A3E-4EFF-8D30-CE85507A0E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E87CD1-5A3E-4EFF-8D30-CE85507A0E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B1668D-3084-4A6C-83A4-C66C1E6C4E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 06-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 07-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B1668D-3084-4A6C-83A4-C66C1E6C4E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE819E23-D787-42AF-8D4E-AF4BC275B315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 07-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE819E23-D787-42AF-8D4E-AF4BC275B315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B75810D-58FC-4C4C-9837-4400912033EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
